--- a/product_upload/packages/9/file.xlsx
+++ b/product_upload/packages/9/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -836,6 +841,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>CO-VALISTA</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-FD22DC28E4C1</t>
         </is>
       </c>
@@ -859,7 +869,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1018,6 +1028,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>VALISTA 320 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-94F49B0F1031</t>
         </is>
       </c>
@@ -1041,7 +1056,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1200,6 +1215,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>VALISTA 160 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-3912BA01EBA6</t>
         </is>
       </c>
@@ -1223,7 +1243,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1394,6 +1414,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>VALISTA 80 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-17EB493483F4</t>
         </is>
       </c>
@@ -1417,7 +1442,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1576,6 +1601,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>IRBETEL 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-DB957008942B</t>
         </is>
       </c>
@@ -1599,7 +1629,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1766,6 +1796,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>RENVELA 800 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-D1116E18AA88</t>
         </is>
       </c>
@@ -1789,7 +1824,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1952,6 +1987,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>NEUROVIT tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-FBDA4E2322C2</t>
         </is>
       </c>
@@ -1975,7 +2015,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2134,6 +2174,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>CO-IRBETEL 325 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-C9C960AA10B9</t>
         </is>
       </c>
@@ -2157,7 +2202,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2316,6 +2361,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>CO-IRBETEL 312.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-2790F4272E3E</t>
         </is>
       </c>
@@ -2339,7 +2389,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2502,6 +2552,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>STIVARGA 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-2FCCFCB70595</t>
         </is>
       </c>
@@ -2525,7 +2580,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2680,6 +2735,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>ACTAMONE 5 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-18E5BA3546B3</t>
         </is>
       </c>
@@ -2703,7 +2763,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2874,6 +2934,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>ZOVIRAX 200MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-CE08FE67943F</t>
         </is>
       </c>
@@ -2897,7 +2962,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3068,6 +3133,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>ZOVIRAX</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-C6C075031194</t>
         </is>
       </c>
@@ -3091,7 +3161,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3262,6 +3332,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>ZOVIRAX</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-35AB14F3B53C</t>
         </is>
       </c>
@@ -3285,7 +3360,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3452,6 +3527,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>ZOVIRAX</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-035730921BA7</t>
         </is>
       </c>
@@ -3475,7 +3555,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3642,6 +3722,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>ZOVIRAX</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-264E55DBF418</t>
         </is>
       </c>
@@ -3665,7 +3750,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3836,6 +3921,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>ZOVIRAX</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-6C1BA0FDB090</t>
         </is>
       </c>
@@ -3859,7 +3949,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4022,6 +4112,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>ZOTRIM SUSP.</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-E349F9A2545B</t>
         </is>
       </c>
@@ -4045,7 +4140,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4216,6 +4311,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>ZOTRIM FORTE TAB.</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-406FCCC31C78</t>
         </is>
       </c>
@@ -4239,7 +4339,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4398,6 +4498,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>ZYNOVATE 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-BB10CF54D6C8</t>
         </is>
       </c>
@@ -4421,7 +4526,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4576,6 +4681,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>ZYNOVATE 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-ADBDE88C48DD</t>
         </is>
       </c>
@@ -4599,7 +4709,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4758,6 +4868,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>ACTAMONE 4 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-81A5E8213D5E</t>
         </is>
       </c>
@@ -4781,7 +4896,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4944,6 +5059,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>AXOR 30 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-52723F30FD66</t>
         </is>
       </c>
@@ -4967,7 +5087,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5126,6 +5246,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>AXOR 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-147DDC55BF91</t>
         </is>
       </c>
@@ -5149,7 +5274,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5312,6 +5437,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>AXOR 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-238A845AAE00</t>
         </is>
       </c>
@@ -5335,7 +5465,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5506,6 +5636,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>ENDOLET 90 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-CCF6967022C7</t>
         </is>
       </c>
@@ -5529,7 +5664,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5700,6 +5835,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>ENDOLET 60 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-755D27748B94</t>
         </is>
       </c>
@@ -5723,7 +5863,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5890,6 +6030,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>ENDOLET 30 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-4A19E489C61E</t>
         </is>
       </c>
@@ -5913,7 +6058,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6072,6 +6217,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>DESOGEST 0.075 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-1D2348E0396A</t>
         </is>
       </c>
@@ -6095,7 +6245,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6262,6 +6412,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>ZYRTEC 10MG F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-EC67F33D94A7</t>
         </is>
       </c>
@@ -6285,7 +6440,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6452,6 +6607,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>ZYRTEC 0.1% ORAL SOLN.</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-73CF3BBA42BE</t>
         </is>
       </c>
@@ -6475,7 +6635,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6634,6 +6794,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>ZYNOVATE 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-A77610290CA3</t>
         </is>
       </c>
@@ -6657,7 +6822,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6816,6 +6981,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>ZYNOVATE 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-F8914393318C</t>
         </is>
       </c>
@@ -6839,7 +7009,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7010,6 +7180,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>WAFI 100 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-CBC74F8EFDB7</t>
         </is>
       </c>
@@ -7033,7 +7208,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7204,6 +7379,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>VOTREX 50 TAB</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-D7B63BF94FCF</t>
         </is>
       </c>
@@ -7227,7 +7407,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7394,6 +7574,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>VOMINORE TAB</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-942EF5588E91</t>
         </is>
       </c>
@@ -7417,7 +7602,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7588,6 +7773,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>VOLTIC -D 50MG DISPERSIBLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-7C1612840C73</t>
         </is>
       </c>
@@ -7611,7 +7801,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7778,6 +7968,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>VOLTIC 50MG E.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-5C2B1A6B0016</t>
         </is>
       </c>
@@ -7801,7 +7996,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7974,6 +8169,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>VOLTAREN RETARD 100MG TAB</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-8FE4B90C3CCA</t>
         </is>
       </c>
@@ -7997,7 +8197,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8168,6 +8368,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>VOLTAREN RETARD 100MG TAB</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-B6BEE13B0E68</t>
         </is>
       </c>
@@ -8191,7 +8396,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8354,6 +8559,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>WAFI 25 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-B845D04EF380</t>
         </is>
       </c>
@@ -8377,7 +8587,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8548,6 +8758,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>WAFI 50 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-769FF4B1338B</t>
         </is>
       </c>
@@ -8571,7 +8786,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8736,6 +8951,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>WATER FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-BA8DAE40F27E</t>
         </is>
       </c>
@@ -8759,7 +8979,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8922,6 +9142,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>WATER FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-606FB80143B1</t>
         </is>
       </c>
@@ -8945,7 +9170,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9104,6 +9329,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>WATER FOR INJ. AMP</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-534543D687D7</t>
         </is>
       </c>
@@ -9127,7 +9357,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9290,6 +9520,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>WATER FOR INJ. AMP</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-491DE72ECAD4</t>
         </is>
       </c>
@@ -9313,7 +9548,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9488,6 +9723,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>VOLTAREN EMULGEL 1%</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-756E9E89ACBD</t>
         </is>
       </c>
@@ -9511,7 +9751,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9674,6 +9914,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>WATER FOR INJ. AMP</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-DC5D65C6808B</t>
         </is>
       </c>
@@ -9697,7 +9942,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9868,6 +10113,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>WATER FOR INJ AMP</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-21A6022FF20F</t>
         </is>
       </c>
@@ -9891,7 +10141,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10058,6 +10308,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>WATER FOR INJ AMP</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-0BE55E181EE6</t>
         </is>
       </c>
@@ -10081,7 +10336,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10244,6 +10499,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>WATENE 0.1% GEL</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-C554C31F1CA2</t>
         </is>
       </c>
@@ -10267,7 +10527,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10430,6 +10690,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>WATENE 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-F4F973C591B9</t>
         </is>
       </c>
@@ -10453,7 +10718,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10612,6 +10877,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>WARTEC 0.15% W-W CREAM</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-91DDC3284284</t>
         </is>
       </c>
@@ -10635,7 +10905,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10790,6 +11060,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>WATER FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-3CE51BCFF606</t>
         </is>
       </c>
@@ -10813,7 +11088,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10984,6 +11259,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>VOLTAREN EMULGEL 1%</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-8B8F602639B2</t>
         </is>
       </c>
@@ -11007,7 +11287,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11164,6 +11444,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>VIVOTIF BERNA CAPS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-DAC692BB617C</t>
         </is>
       </c>
@@ -11187,7 +11472,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11354,6 +11639,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>VISCOR 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-21D6CA537CBF</t>
         </is>
       </c>
@@ -11377,7 +11667,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11536,6 +11826,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>VISCODRIL EXPECTORANT 100ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-8A5857E44E9C</t>
         </is>
       </c>
@@ -11559,7 +11854,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11726,6 +12021,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>VISANNE 2MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-620A967204C2</t>
         </is>
       </c>
@@ -11749,7 +12049,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11916,6 +12216,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>VIRUSTAT 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-C1CC4FE88BF3</t>
         </is>
       </c>
@@ -11939,7 +12244,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12110,6 +12415,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>VIROL</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-C6668A239F7D</t>
         </is>
       </c>
@@ -12133,7 +12443,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12292,6 +12602,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>VIRAZOLE 20MG-MLUPON RECONSTITUTON INHAL</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-EE79883B771F</t>
         </is>
       </c>
@@ -12315,7 +12630,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12478,6 +12793,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>VIVIDRIN 2% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-3BF49B4267FF</t>
         </is>
       </c>
@@ -12501,7 +12821,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12658,6 +12978,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>VITOP CAP</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-D457D6ED533E</t>
         </is>
       </c>
@@ -12681,7 +13006,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12852,6 +13177,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>VITANERVE F.C TAB</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-76E01197E961</t>
         </is>
       </c>
@@ -12875,7 +13205,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13034,6 +13364,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>VOCORT CREAM</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-5487AFB858C1</t>
         </is>
       </c>
@@ -13057,7 +13392,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13210,6 +13545,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>WATER FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-5A270A63C6D3</t>
         </is>
       </c>
@@ -13233,7 +13573,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13390,6 +13730,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>WATER FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-17DA31B59828</t>
         </is>
       </c>
@@ -13413,7 +13758,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13576,6 +13921,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>WATER FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-A08B29D9FA6A</t>
         </is>
       </c>
@@ -13599,7 +13949,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13774,6 +14124,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>XOLAMOL EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-5CD40886B8A2</t>
         </is>
       </c>
@@ -13797,7 +14152,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13972,6 +14327,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>XYLO-MEPHA 0.1% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-35BE13F77C0E</t>
         </is>
       </c>
@@ -13995,7 +14355,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14162,6 +14522,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>XYLOMET Adult nasal drops</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-56EB5ABD2738</t>
         </is>
       </c>
@@ -14185,7 +14550,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14356,6 +14721,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>XYLOMET Peadiatric nasal drops</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-638A8CA1E4C6</t>
         </is>
       </c>
@@ -14379,7 +14749,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14542,6 +14912,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>XYLONOR SPRAY</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-6848F1D87631</t>
         </is>
       </c>
@@ -14565,7 +14940,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14736,6 +15111,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>ZAMUR 500 MG F- C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-AA9A9B56BB4D</t>
         </is>
       </c>
@@ -14759,7 +15139,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14922,6 +15302,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>XYLOPHIL 2% GEL</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-E01159775F85</t>
         </is>
       </c>
@@ -14945,7 +15330,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15112,6 +15497,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>XYZAL 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-2969EF8CE639</t>
         </is>
       </c>
@@ -15135,7 +15525,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15306,6 +15696,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>XOLA OPTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-12EC1AB318D1</t>
         </is>
       </c>
@@ -15329,7 +15724,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15502,6 +15897,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>XERACTAN 20 MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-9539855B5D37</t>
         </is>
       </c>
@@ -15525,7 +15925,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15692,6 +16092,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>XERACTAN 10 MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-89310B50EF9B</t>
         </is>
       </c>
@@ -15715,7 +16120,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15886,6 +16291,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>WINEX 400MG CAP</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-ACB6708B5E58</t>
         </is>
       </c>
@@ -15909,7 +16319,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16076,6 +16486,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>WINEX 200MG CAP</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-9A62288A6734</t>
         </is>
       </c>
@@ -16099,7 +16514,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16266,6 +16681,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>WINEX 100MG\5ML ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-ACBE133B5EBD</t>
         </is>
       </c>
@@ -16289,7 +16709,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16464,6 +16884,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>XALACOM EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-B54FD00A1958</t>
         </is>
       </c>
@@ -16487,7 +16912,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16654,6 +17079,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>WAXSOL</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-578F4960E955</t>
         </is>
       </c>
@@ -16677,7 +17107,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16838,6 +17268,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-F52E601468B3</t>
         </is>
       </c>
@@ -16861,7 +17296,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17022,6 +17457,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-FBFEBA50EA5B</t>
         </is>
       </c>
@@ -17045,7 +17485,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17206,6 +17646,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-95B29E543B8C</t>
         </is>
       </c>
@@ -17229,7 +17674,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17386,6 +17831,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-D273D8503770</t>
         </is>
       </c>
@@ -17409,7 +17859,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17566,6 +18016,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-7B43C82FC19D</t>
         </is>
       </c>
@@ -17589,7 +18044,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17746,6 +18201,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-F6F6AA217F5F</t>
         </is>
       </c>
@@ -17769,7 +18229,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17942,6 +18402,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>XALATAN 50MCG\ML EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-CE68529531D1</t>
         </is>
       </c>
@@ -17965,7 +18430,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18126,6 +18591,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>XANAX 0.5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-12CCD8DB8EF1</t>
         </is>
       </c>
@@ -18149,7 +18619,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18318,6 +18788,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>XENICAL 120MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-3A8B85599FD4</t>
         </is>
       </c>
@@ -18341,7 +18816,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18510,6 +18985,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>XELODA 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-E120F53E2D92</t>
         </is>
       </c>
@@ -18533,7 +19013,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18694,6 +19174,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>XELODA 150MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-E4491AEBDFE5</t>
         </is>
       </c>
@@ -18717,7 +19202,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18882,6 +19367,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>XANAX 0.25 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-CA59ECF81DF2</t>
         </is>
       </c>
@@ -18905,7 +19395,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19076,6 +19566,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>XEFO 8MG TAB</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-28D02E1F37E8</t>
         </is>
       </c>
@@ -19099,7 +19594,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19264,6 +19759,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>XARELTO 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-0E1A279198D5</t>
         </is>
       </c>
@@ -19287,7 +19787,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19459,6 +19959,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>XARELTO 15MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-D148D78081E3</t>
         </is>
@@ -19475,7 +19980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19521,100 +20026,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19646,7 +20156,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19661,92 +20171,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-59084</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>369.76</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>720</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19778,7 +20293,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19793,92 +20308,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-67950</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>493.75</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>721</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19910,7 +20430,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19925,92 +20445,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-84490</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>438.95</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>722</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20042,7 +20567,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20057,92 +20582,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-19025</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>302.08</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>723</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20174,7 +20704,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20189,92 +20719,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-64458</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>204.9</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>724</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20306,7 +20841,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20321,92 +20856,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-38124</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>421.56</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>725</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20438,7 +20978,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20453,92 +20993,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-74006</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>473.38</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>726</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20570,7 +21115,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20585,92 +21130,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-53632</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>156.25</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>727</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20702,7 +21252,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20717,92 +21267,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-11878</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>70.20999999999999</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>728</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20834,7 +21389,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20849,92 +21404,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-33751</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>329.91</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>729</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20966,7 +21526,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20981,92 +21541,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-15389</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>220.19</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>730</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21098,7 +21663,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21113,92 +21678,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-59236</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>25.75</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>731</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21215,7 +21785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21321,6 +21891,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21356,7 +21936,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21421,6 +22001,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-A60D9B7B2EFA</t>
         </is>
@@ -21457,7 +22047,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21522,6 +22112,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-27B8C5226C30</t>
         </is>
@@ -21558,7 +22158,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21623,6 +22223,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-8D039BF08740</t>
         </is>
@@ -21659,7 +22269,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21724,6 +22334,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-57AEF910152D</t>
         </is>
@@ -21760,7 +22380,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21825,6 +22445,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-CF65D79F729B</t>
         </is>
@@ -21861,7 +22491,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21926,6 +22556,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-C03454F3DE3C</t>
         </is>
@@ -21962,7 +22602,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22027,6 +22667,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-8730498E1A70</t>
         </is>
@@ -22063,7 +22713,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22128,6 +22778,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-AA8A041206FF</t>
         </is>
@@ -22164,7 +22824,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22229,6 +22889,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-13446360D022</t>
         </is>
@@ -22265,7 +22935,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22330,6 +23000,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-488244FA6284</t>
         </is>
@@ -22366,7 +23046,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22431,6 +23111,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-7AA1B1E85B06</t>
         </is>
@@ -22467,7 +23157,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22532,6 +23222,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-B2C05E497D1C</t>
         </is>
@@ -22568,7 +23268,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22633,6 +23333,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-84A366DBCBBB</t>
         </is>
@@ -22669,7 +23379,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22734,6 +23444,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-ABC6CE09BE6A</t>
         </is>
@@ -22770,7 +23490,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22835,6 +23555,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-17452823B7CD</t>
         </is>
@@ -22871,7 +23601,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22936,6 +23666,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-7DE7C728179C</t>
         </is>
@@ -22972,7 +23712,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23037,6 +23777,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-589552373FB3</t>
         </is>
@@ -23073,7 +23823,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23138,6 +23888,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-B4F6ABEA5ADB</t>
         </is>
@@ -23174,7 +23934,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23239,6 +23999,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-7D93CD5471D9</t>
         </is>
@@ -23275,7 +24045,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23340,6 +24110,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-FE701B313F05</t>
         </is>

--- a/product_upload/packages/9/file.xlsx
+++ b/product_upload/packages/9/file.xlsx
@@ -686,8 +686,16 @@
           <t>9821413515-695-200315775195</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-VALISTA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CO-VALISTA detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -877,8 +885,16 @@
           <t>6172858283-975-513857135102</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VALISTA 320 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>VALISTA 320 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1064,8 +1080,16 @@
           <t>5857631400-944-900233689239</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VALISTA 160 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VALISTA 160 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1450,8 +1474,16 @@
           <t>8522728980-378-839242414717</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IRBETEL 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>IRBETEL 300 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -2023,8 +2055,16 @@
           <t>5266549952-976-102550556492</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-IRBETEL 325 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CO-IRBETEL 325 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2210,8 +2250,16 @@
           <t>8089928015-451-071866122717</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-IRBETEL 312.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CO-IRBETEL 312.5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2397,8 +2445,16 @@
           <t>0935232529-073-626384935929</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STIVARGA 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>STIVARGA 40 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2588,8 +2644,16 @@
           <t>4953788220-922-771852156039</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACTAMONE 5 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ACTAMONE 5 mg chewable tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -3957,8 +4021,16 @@
           <t>8075451416-068-283176372602</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOTRIM SUSP.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ZOTRIM SUSP. detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4347,8 +4419,16 @@
           <t>7265563923-310-470444502829</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYNOVATE 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ZYNOVATE 0.1% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4534,8 +4614,16 @@
           <t>9214076374-955-055519235131</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYNOVATE 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ZYNOVATE 0.1% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4717,8 +4805,16 @@
           <t>5100837378-821-713923811598</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACTAMONE 4 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ACTAMONE 4 mg chewable tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4904,8 +5000,16 @@
           <t>5198551324-447-849683838097</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AXOR 30 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>AXOR 30 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5095,8 +5199,16 @@
           <t>1078261440-985-205974093666</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AXOR 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>AXOR 40 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5282,8 +5394,16 @@
           <t>6870565283-516-568007364349</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AXOR 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>AXOR 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -6066,8 +6186,16 @@
           <t>5361838608-391-142791563193</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DESOGEST 0.075 mg tablet</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DESOGEST 0.075 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6643,8 +6771,16 @@
           <t>8462774952-958-698524537844</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYNOVATE 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ZYNOVATE 0.1% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6830,8 +6966,16 @@
           <t>8383207252-644-720243348490</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYNOVATE 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ZYNOVATE 0.1% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -8404,8 +8548,16 @@
           <t>3401125552-748-530672286315</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WAFI 25 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>WAFI 25 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8987,8 +9139,16 @@
           <t>3451945768-669-258254104771</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>WATER FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9178,8 +9338,16 @@
           <t>1037046190-158-827856253828</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR INJ. AMP</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>WATER FOR INJ. AMP detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9365,8 +9533,16 @@
           <t>5423750358-106-164759062461</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR INJ. AMP</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>WATER FOR INJ. AMP detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9759,8 +9935,16 @@
           <t>9003982581-644-484199298794</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR INJ. AMP</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>WATER FOR INJ. AMP detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -10535,8 +10719,16 @@
           <t>2929802171-285-361333999624</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATENE 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>WATENE 0.1% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10726,8 +10918,16 @@
           <t>3585200832-083-984099284623</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WARTEC 0.15% W-W CREAM</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>WARTEC 0.15% W-W CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10913,8 +11113,16 @@
           <t>1732303134-657-921524621821</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>WATER FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11295,8 +11503,16 @@
           <t>5835307079-997-935248394013</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIVOTIF BERNA CAPS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>VIVOTIF BERNA CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11480,8 +11696,16 @@
           <t>3144215623-078-201918603647</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VISCOR 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>VISCOR 20MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11675,8 +11899,16 @@
           <t>7323294895-936-917271068993</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VISCODRIL EXPECTORANT 100ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>VISCODRIL EXPECTORANT 100ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11862,8 +12094,16 @@
           <t>8380291668-952-952853881236</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VISANNE 2MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>VISANNE 2MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12451,8 +12691,16 @@
           <t>8352254250-882-994038614758</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRAZOLE 20MG-MLUPON RECONSTITUTON INHAL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>VIRAZOLE 20MG-MLUPON RECONSTITUTON INHAL detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12638,8 +12886,16 @@
           <t>9016499830-277-623457548890</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIVIDRIN 2% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>VIVIDRIN 2% EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12829,8 +13085,16 @@
           <t>3785172169-445-247724570176</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VITOP CAP</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>VITOP CAP detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13213,8 +13477,16 @@
           <t>7004013760-897-137221231017</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VOCORT CREAM</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>VOCORT CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13400,8 +13672,16 @@
           <t>2541657655-376-988096363336</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>WATER FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13581,8 +13861,16 @@
           <t>9814317452-109-210290618426</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>WATER FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13766,8 +14054,16 @@
           <t>1583707614-654-159268300529</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>WATER FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14757,8 +15053,16 @@
           <t>2920122669-649-313224989136</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XYLONOR SPRAY</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>XYLONOR SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15147,8 +15451,16 @@
           <t>0538311293-152-062562349674</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XYLOPHIL 2% GEL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>XYLOPHIL 2% GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -17115,8 +17427,16 @@
           <t>4281564824-404-571971284788</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>WATER FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17304,8 +17624,16 @@
           <t>1172377315-428-418148867845</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>WATER FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17493,8 +17821,16 @@
           <t>5106465045-492-334384700653</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>WATER FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17682,8 +18018,16 @@
           <t>9332763593-780-388334713711</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>WATER FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17867,8 +18211,16 @@
           <t>8297411176-701-129903104131</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>WATER FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18052,8 +18404,16 @@
           <t>3646907264-970-845718615515</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>WATER FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18438,8 +18798,16 @@
           <t>2976405793-111-640489313249</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XANAX 0.5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>XANAX 0.5 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -19021,8 +19389,16 @@
           <t>9190431353-131-988430521940</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XELODA 150MG TABLET</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>XELODA 150MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/9/file.xlsx
+++ b/product_upload/packages/9/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20402,7 +20402,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22161,7 +22161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22242,40 +22242,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22355,38 +22360,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>461.5</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-A60D9B7B2EFA</t>
         </is>
@@ -22466,38 +22476,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>322.26</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-27B8C5226C30</t>
         </is>
@@ -22577,38 +22592,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>365.13</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-8D039BF08740</t>
         </is>
@@ -22688,38 +22708,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>448.97</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-57AEF910152D</t>
         </is>
@@ -22799,38 +22824,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>348.53</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-CF65D79F729B</t>
         </is>
@@ -22910,38 +22940,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>313.59</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-C03454F3DE3C</t>
         </is>
@@ -23021,38 +23056,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>127.36</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-8730498E1A70</t>
         </is>
@@ -23132,38 +23172,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>276.56</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-AA8A041206FF</t>
         </is>
@@ -23243,38 +23288,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>464.31</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-13446360D022</t>
         </is>
@@ -23354,38 +23404,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>388.04</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-488244FA6284</t>
         </is>
@@ -23465,38 +23520,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-7AA1B1E85B06</t>
         </is>
@@ -23576,38 +23636,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-B2C05E497D1C</t>
         </is>
@@ -23687,38 +23752,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>410.9</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-84A366DBCBBB</t>
         </is>
@@ -23798,38 +23868,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>212.53</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-ABC6CE09BE6A</t>
         </is>
@@ -23909,38 +23984,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>478.04</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-17452823B7CD</t>
         </is>
@@ -24020,38 +24100,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>200.24</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-7DE7C728179C</t>
         </is>
@@ -24131,38 +24216,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>446.76</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-589552373FB3</t>
         </is>
@@ -24242,38 +24332,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>222.22</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-B4F6ABEA5ADB</t>
         </is>
@@ -24353,38 +24448,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>256.27</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-7D93CD5471D9</t>
         </is>
@@ -24464,38 +24564,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>100.46</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-FE701B313F05</t>
         </is>
